--- a/SHET/gzsign1.xlsx
+++ b/SHET/gzsign1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7D3830-4D2A-46AA-AFEF-6D42A4698B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4A4B95-111A-40A7-A002-3F71575ACDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -29,39 +29,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Номер</t>
-  </si>
-  <si>
-    <t>Обозначение</t>
-  </si>
-  <si>
-    <t>Результат</t>
-  </si>
-  <si>
-    <t>ква</t>
-  </si>
-  <si>
-    <t>пав</t>
-  </si>
-  <si>
-    <t>апап</t>
-  </si>
-  <si>
-    <t>Основные параметры</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="19">
   <si>
     <t>Название таблицы</t>
   </si>
   <si>
-    <t>Основные параметры настройки</t>
-  </si>
-  <si>
     <t>Тэг</t>
   </si>
   <si>
-    <t>Table1</t>
+    <t>Режим</t>
+  </si>
+  <si>
+    <t>ГЗ АТ сигн/ ГЗ сигн 1 цепь: Срабатывание контакта</t>
+  </si>
+  <si>
+    <t>ГЗ АТ сигн/ ГЗ сигн 1 цепь: Вывод</t>
+  </si>
+  <si>
+    <t>ГЗ АТ сигн: Отключение</t>
+  </si>
+  <si>
+    <t>ГЗ АТ сигн: Срабатывание</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>ГЗ АТ сигн/ Перевод ГЗ АТ сигн на отключение</t>
+  </si>
+  <si>
+    <t>gzsign1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверка правильности работы сигнальной ступени ГЗ </t>
+  </si>
+  <si>
+    <t>Сигнал</t>
+  </si>
+  <si>
+    <t>ФК</t>
+  </si>
+  <si>
+    <t>ЖС</t>
+  </si>
+  <si>
+    <t>X:161, X:221</t>
+  </si>
+  <si>
+    <t>X:75, X:79</t>
+  </si>
+  <si>
+    <t>Срабатывание выходного реле при введеном SA1</t>
+  </si>
+  <si>
+    <t>Воздействие</t>
   </si>
 </sst>
 </file>
@@ -97,9 +121,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -382,68 +407,169 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="46.85546875" customWidth="1"/>
+    <col min="1" max="1" width="49.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B1:C1"/>
+  <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -460,15 +586,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
